--- a/artfynd/A 14089-2025 artfynd.xlsx
+++ b/artfynd/A 14089-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124090488</v>
+        <v>124090502</v>
       </c>
       <c r="B2" t="n">
         <v>57507</v>
@@ -715,7 +715,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571133</v>
+        <v>571127</v>
       </c>
       <c r="R2" t="n">
-        <v>6427742</v>
+        <v>6427773</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124090502</v>
+        <v>124090488</v>
       </c>
       <c r="B3" t="n">
         <v>57507</v>
@@ -836,7 +836,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571127</v>
+        <v>571133</v>
       </c>
       <c r="R3" t="n">
-        <v>6427773</v>
+        <v>6427742</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 14089-2025 artfynd.xlsx
+++ b/artfynd/A 14089-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124090488</v>
+        <v>124090502</v>
       </c>
       <c r="B2" t="n">
         <v>57529</v>
@@ -715,7 +715,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571133</v>
+        <v>571127</v>
       </c>
       <c r="R2" t="n">
-        <v>6427742</v>
+        <v>6427773</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124090502</v>
+        <v>124090488</v>
       </c>
       <c r="B3" t="n">
         <v>57529</v>
@@ -836,7 +836,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571127</v>
+        <v>571133</v>
       </c>
       <c r="R3" t="n">
-        <v>6427773</v>
+        <v>6427742</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 14089-2025 artfynd.xlsx
+++ b/artfynd/A 14089-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124090502</v>
+        <v>124090488</v>
       </c>
       <c r="B2" t="n">
         <v>57529</v>
@@ -715,7 +715,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571127</v>
+        <v>571133</v>
       </c>
       <c r="R2" t="n">
-        <v>6427773</v>
+        <v>6427742</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124090488</v>
+        <v>124090502</v>
       </c>
       <c r="B3" t="n">
         <v>57529</v>
@@ -836,7 +836,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571133</v>
+        <v>571127</v>
       </c>
       <c r="R3" t="n">
-        <v>6427742</v>
+        <v>6427773</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 14089-2025 artfynd.xlsx
+++ b/artfynd/A 14089-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,6 +915,122 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129140896</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hagaberg, Hagaberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>571145</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6427767</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 14089-2025 artfynd.xlsx
+++ b/artfynd/A 14089-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129140896</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57738</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14089-2025 artfynd.xlsx
+++ b/artfynd/A 14089-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129140896</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14089-2025 artfynd.xlsx
+++ b/artfynd/A 14089-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>129140896</v>
       </c>
       <c r="B4" t="n">
-        <v>57740</v>
+        <v>57743</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 14089-2025 artfynd.xlsx
+++ b/artfynd/A 14089-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124090488</v>
+        <v>129140896</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,7 +710,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>571133</v>
+        <v>571145</v>
       </c>
       <c r="R2" t="n">
-        <v>6427742</v>
+        <v>6427767</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,19 +791,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124090502</v>
+        <v>124090488</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -836,7 +826,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>571127</v>
+        <v>571133</v>
       </c>
       <c r="R3" t="n">
-        <v>6427773</v>
+        <v>6427742</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,27 +907,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129140896</v>
+        <v>124090502</v>
       </c>
       <c r="B4" t="n">
-        <v>57743</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -952,7 +942,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -961,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>571145</v>
+        <v>571127</v>
       </c>
       <c r="R4" t="n">
-        <v>6427767</v>
+        <v>6427773</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,22 +981,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,6 +1020,122 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129140944</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hagaberg, Hagaberg, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>571151</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6427730</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
